--- a/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
+++ b/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
@@ -14,9 +14,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'5-Week Plan'!$A$8:$G$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'5-Week Plan'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'5-Week Plan'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'References'!$A$4:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'References'!$A$4:$G$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'References'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'References'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'References'!$A$1:$G$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -135,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -185,12 +185,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00CBD5DF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -249,6 +255,13 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -647,7 +660,7 @@
           <t>计划周期</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>2026-08-31 至 2026-09-30；22 个常规学习日</t>
         </is>
@@ -664,7 +677,7 @@
           <t>能力主线</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Python -&gt; RAG -&gt; Tool / Single-Agent Harness -&gt; MCP -&gt; Reliability &amp; Evals</t>
         </is>
@@ -681,7 +694,7 @@
           <t>统一实践场景</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>只读 Requirement Grounding Agent：基于冻结文档检索、引用、拒答，并通过 Tool 与 MCP 接入</t>
         </is>
@@ -698,7 +711,7 @@
           <t>执行基线</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Python 3.12；MCP 2026-07-28 为主线，2025-11-25 做一次兼容对照；模型、SDK 与项目源码执行时冻结版本</t>
         </is>
@@ -709,6 +722,23 @@
       <c r="F6" s="18" t="n"/>
       <c r="G6" s="18" t="n"/>
     </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>横切重点</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Prompt engineering  |  Agent memory  |  MCP / Skills 安装与调度  |  AI SDLC  |  VS Code Codex / Cline</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+    </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -746,7 +776,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="196" customHeight="1">
+    <row r="9" ht="244" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>W12
@@ -762,7 +792,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>从 TypeScript 迁移到 Python AI 工程，建立复杂代码阅读、异步生命周期、资源清理和模型客户端诊断能力。</t>
+          <t>从 TypeScript 迁移到 Python AI 工程，建立复杂代码阅读、异步生命周期、资源清理、Prompt 基线和 coding-agent 使用能力。</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -772,35 +802,43 @@
 • 异常链、context manager、sync/async 边界
 • task、timeout、cancellation、pytest
 • HTTP/streaming 与结构化输入输出
-• Bub turn/hook/tape/context、model/tool/channel</t>
+• Prompt 的 instructions/input/examples/context/output 边界与版本
+• Bub turn/hook/tape/context、model/tool/channel
+• VS Code Codex/Cline 的 context、规则、权限、计划与验证面</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>• 建立项目基线与冒烟测试
 • 冻结 Bub、DeepSeek Harness 来源版本
+• 在 VS Code 记录 Codex/Cline 版本、provider、权限与 AGENTS.md 加载
 • 跟踪 Bub 一次完整 turn 主链并写阅读报告
+• 建立版本化 prompt v0
 • 真实调用 DeepSeek 与最小工具
 • 分别触发 timeout、cancellation，并检查残留 task/连接
+• 本人先独立诊断并冻结答案，再由 VS Code Codex/Cline 同题只读 review
 • 盘点 W13 corpus 规模与排除类别</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
           <t>• 口述 TS -&gt; Python 对应关系与 Python 特有语义
-• 诊断一段未提前见过的异步/资源管理代码
-• 阅读报告区分调用顺序、职责、状态来源、源码事实与待验证行为
+• prompt v0 能关联任务、模型、输入边界与变更理由
+• 本人陌生代码诊断在 agent 介入前已冻结
+• 对照两种 coding-agent 的 context、权限、扩展和验证方式
+• 两端使用同一输入和成功条件，不以单次输出做排行榜
 • W14 D1 延迟重建 Bub/Python 调用链</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
           <t>不进入 RAG、完整 Agent loop、MCP 或 UI。
-交接：Python 项目与模型 client 可运行；Bub 报告未完成不阻塞 W13。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="196" customHeight="1">
+实操只使用已安装的 VS Code Codex 26.5825.51511 与 Cline 4.1.16；Claude Code 受防火墙限制，Codex App 不支持 Intel，均不作为依赖。
+两端同题 hands-on 必做，总投入 60-90 分钟。交接：Python/model client 可运行；prompt v0 已版本化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="224" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>W13
@@ -822,8 +860,9 @@
         <is>
           <t>• ingestion、预处理、chunking、metadata
 • full-context、中文 BM25、dense retrieval
-• 本地多语言 embedding 候选与硬件实测
-• citation、abstention、context budget
+• multilingual-e5-small、中文回退候选与 Intel x86 runtime 门禁
+• grounding prompt、citation、abstention、context budget
+• RAG knowledge 与 Agent memory 的职责差异
 • dev/holdout 隔离与逐题失败分析
 • hybrid/RRF 仅作条件项</t>
         </is>
@@ -834,27 +873,32 @@
 • 本人冻结题目、标签、指标、阈值和通过标准
 • 建立 full-context 质量上限锚点
 • 分别跑通 BM25 与 dense 基线
-• 记录逐题 retrieval/generation 失败、延迟、token、cache hit/miss 成本
+• 复用 Python 3.12，以 onnxruntime==1.23.2 + 发布者 fp32 文件验证 x86 基线；torch==2.2.2 仅作兼容回退
+• 冻结 wheel/hash、runtime/model revision、E5 前缀/归一化/截断，并记录冷启动、吞吐、p50/p95、峰值 RSS 与全量估算
+• 量化仅作同一冻结小样本的条件对照
+• 冻结 grounding/citation/abstention prompt 边界
+• 记录 retrieval、context assembly、prompt、generation 的逐题失败与成本
 • 收口时运行一次 holdout</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
           <t>• 能解释 ingestion -&gt; retrieval -&gt; context -&gt; generation -&gt; eval 边界
-• 对每道失败题给出分层归因与下一实验
+• 不把索引、检索结果、session state 或 trace 混称为 memory
+• 对每道失败题给出 retrieval/context/prompt/generation 分层归因
 • holdout 未被日常调参污染
 • W15 D1 延迟重建确定性 retrieval 数据流</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>reranker、GraphRAG、向量数据库不进入主线。
-本地 embedding 未通过速度/质量门时改用更小模型或第三方 API。
-交接：可用 BM25 入口 + 冻结 eval；dense 未调完不阻塞 W14。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="196" customHeight="1">
+          <t>reranker、GraphRAG、向量数据库和本地生成模型不进入主线。
+只使用已核对到 CPython 3.12/macOS x86_64 wheel 的固定版本；不解析到最新版、不源码编译。安装或资源/质量门失败时改用 embedding API，BM25 与冻结 eval 保留，dense 不阻塞 W14。
+交接：可用 BM25 入口 + 冻结 eval。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="248" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>W14
@@ -870,47 +914,50 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>将 RAG 暴露为只读工具，在显式单 Agent harness 中掌握控制流、工具交互、trace、verifier 与多 trial。</t>
+          <t>将 RAG 暴露为只读工具，在显式单 Agent harness 中掌握控制流、Prompt、工具交互、有界 session state、memory 边界、trace、verifier 与多 trial。</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>• structured output 与 function calling
+          <t>• structured output、function calling 与工具描述
+• system/developer prompt、输入上下文和 injection 边界
 • 参数验证、工具失败、取消与权限边界
+• working context / session state / durable memory / RAG / trace
+• session isolation/reset、context budget 与 compaction/eviction
+• durable memory 的 TTL、delete、隐私、陈旧与投毒边界
 • loop 状态、终止、停滞与人工交还
-• context/state/trace、JSONL trace、replay
-• 外部 verifier、trial 与模型行为观测
-• DeepSeek V4 thinking + tool calls
-• DeepSeek Harness lifecycle/session/tool pipeline</t>
+• JSONL trace、replay、verifier、trial</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>• 本人冻结任务级工具语义、预算、停止/停滞、verifier 与 eval task
-• 实现一个只读 retrieval tool 与最小 harness
-• 落盘脱敏 trace，完成 deterministic replay
-• 对同一任务执行多 trial 并分析失败
+          <t>• 本人冻结工具语义、预算、停止/停滞、state/memory policy、verifier 与 eval task
+• 实现只读 retrieval tool 与最小 harness
+• 对冻结 dev task 只改变一个 prompt 因素并重跑相同 eval
+• 完成有界 session state 的 write/read/reset/isolation 与一次 context compaction/eviction 观察
+• 落盘脱敏 trace，完成 deterministic replay 与多 trial
 • 对照抽样 DeepSeek Harness
-• 条件项：OpenAI Agents SDK compatibility spike，最多半天</t>
+• 条件项：OpenAI Agents SDK spike，最多半天</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>• 解释 model、tool、harness、MCP、verifier 的职责差异
-• replay 可复现确定性部分；模型变化不冒充回归失败
-• trace 足以定位工具、控制层、检索或模型失败
+          <t>• 解释 model、prompt、tool、session state、durable memory、RAG、harness、MCP、verifier 的职责差异
+• prompt 前后比较只改变一个因素并保留版本
+• session reset/isolation 是确定性证据，模型复述差异不是通过标准
+• replay 可复现确定性部分；trace 足以分层定位失败
 • W16 D1 延迟重建 harness 确定性部分</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>不做 multi-agent、长期 memory、写工具或自动部署。
-SDK spike 跑不通即停止，不写 adapter，不作为验收依赖。
-交接：只读 tool + trace + verifier 入口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="196" customHeight="1">
+          <t>不做 multi-agent、持久/向量 memory、写工具或自动部署。
+Prompt + session state/context 实验合计半天；超时先砍 SDK spike 与额外源码抽样。
+交接：只读 tool + trace + verifier + session reset/isolation。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="248" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>W15
@@ -926,47 +973,49 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>从原始消息理解 MCP 的体系、角色、协议、transport、工具/资源交互和代际兼容。</t>
+          <t>从原始消息理解 MCP，并掌握 MCP/Skills 在 coding agent 中的发现、配置、信任、安装与生命周期边界。</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>• host/client/server 与 JSON-RPC
+          <t>• host/client/server、JSON-RPC 与两代协议
 • server/discover、per-request _meta 与能力
-• stdio、Streamable HTTP 边界
-• tools/list/call、resources/list/read
-• MRTR、resultType、input_required
-• JSON-RPC error / isError / 中间态
-• ttlMs/cacheScope、错误码与 deprecated 迁移</t>
+• stdio、tools、resources、MRTR 与三层错误
+• ttlMs/cacheScope、错误码与 deprecated 迁移
+• MCP vs Skill vs project instructions
+• local/project/user scope、来源信任、版本、权限、启停、升级、移除
+• 调度属于 harness/orchestrator，不属于 MCP core</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
           <t>• 用 Python SDK 建现代 stdio server/client
-• 通过自建 client 调 tools/resources；Inspector 可用时并行检查，否则记录兼容性结果
-• 触发协议版本不匹配并完成诊断
-• 同一 tools/call 分别抓取 2026-07-28 与 2025-11-25 消息流并 diff
-• SDK 使用 auto 探测现代协议；legacy 模式只用于兼容实验</t>
+• 自建 client 调 tools/resources；Inspector 可用时并行检查
+• 触发协议版本不匹配并诊断
+• 同一 tools/call 抓取 2026-07-28 与 2025-11-25 消息流并 diff
+• 在 VS Code Codex 与 Cline 分别注册、调用、禁用和移除同一只读 server
+• 检查一个小 Skill 的 SKILL.md，完成发现、触发、禁用和移除；产品版本未提供入口时只记录能力边界</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
           <t>• 从消息层解释发现、调用、返回与失败
-• 能说明现代 server/discover/_meta 与旧 initialize/session 的差异
-• 区分三层错误语义与 MRTR 中间态
-• 能定位 protocol version、schema、tool 与 transport 问题
+• 说明现代 server/discover/_meta 与旧 initialize/session 的差异
+• 区分 MCP、Skill、instructions、hook/automation 的职责
+• 能说明 scope、信任、版本和权限选择
+• 产品客户端调用只证明互操作，协议版本以 Python SDK 原始消息为准
 • 10/12 延迟重建 MCP 新旧主链</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>旧版只 hands-on 一次；roots/sampling/logging 只学 deprecated 与迁移。
-远程授权、Tasks 扩展、完整 HTTP 实践为 stretch。
-交接：stdio server + tools/resources 可调用 + 新旧消息 diff。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196" customHeight="1">
+          <t>旧版只 hands-on 一次；产品客户端与 Skill 生命周期合计 90 分钟。
+只使用现有 VS Code Codex/Cline，不安装 Claude Code、不使用 Codex App。Cline 定时调度不适用于 VS Code 扩展；W16 以 multi-trial runner 实践调度语义。
+远程授权、Tasks、完整 HTTP 为 stretch。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="238" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>W16
@@ -982,51 +1031,55 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>将 RAG、Agent 与 MCP 串成可观察、可归因、可回归的最小链路，不新增产品功能。</t>
+          <t>将 RAG、Agent 与 MCP 串成可观察、可归因、可回归的最小链路，并掌握 Prompt/memory 回归、运行调度与 AI SDLC。</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>• eval task、trial、grader、trace 与 outcome
-• context engineering 与 context budget
-• 故障注入、分层归因、回归与版本冻结
-• 非确定性模型行为 vs 确定性 harness 逻辑
-• 隐私、密钥、语料与 trace 边界</t>
+• Prompt/context engineering 与版本回归
+• stale/poisoned memory、session isolation 与 reset
+• foreground/background/recurring/batch、并发、重试、幂等、取消
+• 故障注入、分层归因与版本冻结
+• AI SDLC：spec、权限、diff review、test/eval、安全、release/rollback、provenance
+• 非确定性模型行为 vs 确定性 harness 逻辑</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>• D1：连接 RAG -&gt; Agent -&gt; MCP，冻结可重复基线
-• D2：执行本人设计的故障注入并完成分层归因
-• D3：运行 holdout 回归、确定性重建与事实收口
-• 汇总多 trial 的质量、错误、延迟、token 与成本
-• 写明后续未验证项和下一入口</t>
+          <t>• D1：连接 RAG -&gt; Agent -&gt; MCP，冻结 prompt/memory/调度基线
+• D2：注入 stale durable-memory fixture 或跨 session state 泄漏，并覆盖重试/取消/幂等的一条失败路径
+• D3：运行 holdout、prompt regression、确定性重建与事实收口
+• 复用 multi-trial runner 观察有界调度，不建调度服务
+• 用 60-90 分钟让一个小型白名单变更走完 spec -&gt; AI change -&gt; review -&gt; test/eval -&gt; release/rollback 闭环</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>• 不以单次成功替代可靠性结论
-• 每个失败可归到 retrieval、tool、harness、MCP、model 或 verifier
-• 同版本/同输入下确定性部分可重放
-• 独立重建控制流、trace schema、verifier 边界与 MCP 主链</t>
+          <t>• 不以单次成功或主观 prompt 改善替代可靠性结论
+• memory 泄漏/陈旧状态可被检测、隔离或 reset
+• 每个失败可归到 retrieval、prompt/context、memory、tool、harness、MCP、model 或 verifier
+• 同输入下确定性部分可重放
+• AI 生成代码有规格、所有权、验证、版本与回滚证据</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>不增加 FastAPI、Docker/CI、UI 或新工具。
-假期额外时间只回填 stretch，不回填主线。
-收口：更新状态、债务与后续重建入口。</t>
+          <t>不增加 scheduler、持久/向量 memory、FastAPI、Docker/CI、UI 或新产品。
+AI SDLC timebox 60-90 分钟并复用综合链路；不以生成代码量为目标。
+假期只回填 stretch。收口：更新状态、债务与重建入口。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A8:G13"/>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
@@ -1043,12 +1096,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1067,10 +1120,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>链接于 2026-08-31 核实；执行时仍需记录模型 alias/快照、SDK/包版本和项目 commit。</t>
+          <t>链接于 2026-08-31 核实。每周先读 2-4 条「核心入口」；Hands-on/实验查阅随任务打开，其余作为资料库，不顺序通读。</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1164,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1134,7 +1187,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>核心入口</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -1148,7 +1201,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1171,7 +1224,7 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>核心入口</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -1185,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1208,7 +1261,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>实验查阅</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1222,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1245,7 +1298,7 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>实验查阅</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -1259,7 +1312,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1282,7 +1335,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>实验查阅</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1296,7 +1349,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>W12</t>
@@ -1319,7 +1372,7 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>必读</t>
+          <t>核心入口</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -1333,1425 +1386,2185 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Prompt engineering</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Prompt engineering, OpenAI API</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>指令/输入/样例/context 分区、Prompt 代码化版本与变更前 eval</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/guides/prompt-engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>VS Code Codex</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Best practices, Codex</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>OpenAI 官方指南</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>在 IDE 扩展中核对 context、Prompt、AGENTS.md、权限、review 与验证边界</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>https://learn.chatgpt.com/guides/best-practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>VS Code Codex</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Codex IDE extension</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>OpenAI 官方文档</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>编辑器 context、只读 review、diff 与权限；不依赖 Codex App</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>https://learn.chatgpt.com/docs/codex/ide</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>W12/W16</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Cline workflow</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Plan &amp; Act Mode, Cline</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>Plan-only review、Act 权限与验证边界；用于同题任务和 AI SDLC</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/core-workflows/plan-and-act</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>RAG</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Introducing Contextual Retrieval</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>dense + BM25、contextual chunk、fusion 与 rerank 的整体图景</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/contextual-retrieval</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>RAG eval</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Ragas: Automated Evaluation of Retrieval Augmented Generation</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>论文</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>retrieval、faithfulness 与 generation 的评估维度</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2309.15217</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>RAG eval</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Ragas documentation</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>项目文档</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>按需</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>指标与实验 API 参考；不作为本周验收依赖</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>https://docs.ragas.io/en/stable/</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Embedding</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>BAAI/bge-m3</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>模型卡</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>候选</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>本地多语言 embedding 候选、能力与资源要求</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>https://huggingface.co/BAAI/bge-m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>intfloat/multilingual-e5-small</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>发布者模型卡</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>默认候选</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Intel x86 CPU 多语言基线；核对前缀、归一化、截断、模型 revision 与 ONNX 文件</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/intfloat/multilingual-e5-small</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Hybrid retrieval</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Hybrid and Multi-Stage Queries, Qdrant</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Intel CPU inference</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Speeding up Inference, Sentence Transformers</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>RRF/DBSF 与多阶段检索参考；不要求部署 Qdrant</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
-        <is>
-          <t>https://qdrant.tech/documentation/search/hybrid-queries/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>比较 CPU ONNX/fp32/量化；CPU 不使用 fp16/bf16 假设，必须在冻结语料实测</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>https://www.sbert.net/docs/sentence_transformer/usage/efficiency.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Intel runtime</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>PyTorch macOS x86 builds deprecation</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>PyTorch 官方说明</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>环境边界</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>确认 2.2 之后不再提供 macOS x86 二进制；D1 不假设最新 PyTorch 可安装</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>https://dev-discuss.pytorch.org/t/pytorch-macos-x86-builds-deprecation-starting-january-2024/1690</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Intel runtime</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>ONNX Runtime 1.23.2 release files</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>PyPI 发布物</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>环境边界</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>CPython 3.12/macOS x86_64 wheel 已存在；作为首选 runtime，D1 冻结 wheel/hash</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/onnxruntime/1.23.2/#files</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Intel runtime</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>PyTorch 2.2.2 release files</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>PyPI 发布物</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>回退候选</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>CPython 3.12/macOS x86_64 wheel 已存在；仅作兼容回退，不解析到后续版本</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/torch/2.2.2/#files</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Embedding fallback</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>BAAI/bge-small-zh-v1.5</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>发布者模型卡</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>回退候选</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>仅作中文检索回退对照；不替代默认多语言 E5，也不预设质量通过</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/BAAI/bge-small-zh-v1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>W13/W14</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Model baseline</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Models &amp; Pricing, DeepSeek API</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>版本冻结</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>记录 V4 alias 对应快照、能力、上下文与成本</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/quick_start/pricing/</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>W13/W14</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Model version</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Change Log, DeepSeek API</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>版本冻结</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>核对模型发布、alias 与行为变更历史</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/updates/</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Agent foundations</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Building agents</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>官方学习轨</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Agent 定义、工具、guardrail 与实作主线</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>https://developers.openai.com/tracks/building-agents</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Tool calling</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Function calling, OpenAI API</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>工具 schema、调用/回传循环、strict output 与错误边界</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/function-calling</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Agents SDK</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Agents SDK Quickstart, OpenAI API</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Spike</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>半天 compatibility spike 的 SDK 入口</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/agents/quickstart</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>W14/W16</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Guardrails</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Guardrails and human review, OpenAI API</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>输入/输出 guardrail、工具审批与人工复核边界</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/agents/guardrails-approvals</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Agent patterns</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Building effective agents</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>基础阅读</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>workflow/agent 区分、简单 loop、停止与透明性原则</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/building-effective-agents</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Tool protocol</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Tool use with Claude</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>必读（区域可用）</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>区域条件</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>tool schema、tool_use/tool_result 往返与错误处理；区域不可用时使用下一行官方 Cookbook</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>https://platform.claude.com/docs/en/agents-and-tools/tool-use/overview</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Tool protocol</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Claude Cookbooks: Tool use</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>官方示例仓库</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>替代入口</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>官方文档区域不可访问时，查看 Python 工具调用与 tool_result 往返示例</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>https://github.com/anthropics/claude-cookbooks/tree/main/tool_use</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Tool design</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Writing effective tools for agents — with agents</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>工具边界、描述、返回上下文、token 效率与 tool eval</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/writing-tools-for-agents</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>W14/W16</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Harness</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Effective harnesses for long-running agents</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>进度状态、失败模式、终止与真实环境验证</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/effective-harnesses-for-long-running-agents</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>Thinking Mode, DeepSeek API</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>thinking/non-thinking、reasoning_content 与 tool calls 组合约束</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G35" s="19" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/guides/thinking_mode/</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Tool Calls, DeepSeek API</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Chat Completions 工具 schema、调用/回传与 strict mode</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/guides/tool_calls/</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>Using the Responses API, DeepSeek</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Spike</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>Responses 兼容范围、流事件和支持/忽略的工具类型</t>
         </is>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>https://api-docs.deepseek.com/guides/responses_api/</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Harness reference</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>DeepSeek Harness</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>官方项目</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>developer preview 项目入口；执行时锁定 commit</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>https://github.com/deepseek-ai/deepseek-harness</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Harness reference</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>DeepSeek Harness Architecture</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>官方项目文档</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>按需</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>plugin、model、tool、session 与 agent-loop 架构</t>
         </is>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>https://github.com/deepseek-ai/deepseek-harness/blob/master/docs/architecture.md</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Conversation state, OpenAI API</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>消息、tool call/output、response chaining 与 durable conversation state 的边界</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/guides/conversation-state</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Compaction, OpenAI API</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>长对话 context 压缩、threshold、质量/成本/延迟与状态承接</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>https://developers.openai.com/api/docs/guides/compaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Memory tool, Claude Platform</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>区域条件</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>client-side durable memory 的 read/write/update/delete、隔离与按需读取</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>https://platform.claude.com/docs/en/agents-and-tools/tool-use/memory-tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>W14/W16</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Memory Bank, Cline</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>比较文件型跨 session 项目上下文与 runtime session state、durable memory、RAG 和 trace</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/best-practices/memory-bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>W14/W16</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Prompt engineering</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Prompt engineering overview, Claude Platform</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>区域条件</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>先冻结成功标准与 empirical tests，再优化 Prompt；模型专属建议需实测</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>https://platform.claude.com/docs/en/build-with-claude/prompt-engineering/overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>MCP foundations</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>Architecture, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>host/client/server、stateless 与安全边界</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G45" s="19" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/architecture</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>MCP migration</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>Key Changes, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>2025-11-25 到 2026-07-28 的完整差异</t>
         </is>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/changelog</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>MCP discovery</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>Discovery, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>server/discover、per-request metadata 与 stdio fallback</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/server/discover</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>MCP tools</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>Tools, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>tools/list、tools/call、schema 与结果/错误语义</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/server/tools</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>MCP resources</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>Resources, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>resources/list/read、URI 与缓存语义</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="G49" s="19" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/server/resources</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>MCP transport</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>Transports: Overview, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>stdio、Streamable HTTP、framing、metadata 与取消</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/basic/transports</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>MCP lifecycle</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>Deprecated Features, MCP 2026-07-28</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>官方规范</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>roots、sampling、logging、DCR、HTTP+SSE 的迁移路径</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/specification/2026-07-28/deprecated</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>MCP SDK</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>MCP Python SDK</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>官方 SDK</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>现代 server/client 的 Python 实践入口</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>https://py.sdk.modelcontextprotocol.io/</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>MCP compatibility</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>Protocol versions, MCP Python SDK</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>官方 SDK 文档</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>auto/legacy/pin 双代协商与消息流实验依据</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G53" s="19" t="inlineStr">
         <is>
           <t>https://py.sdk.modelcontextprotocol.io/protocol-versions/</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>MCP MRTR</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>Multi-round-trip requests, MCP Python SDK</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>官方 SDK 文档</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>实验查阅</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
         <is>
           <t>input_required、inputResponses 与 requestState</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G54" s="20" t="inlineStr">
         <is>
           <t>https://py.sdk.modelcontextprotocol.io/handlers/multi-round-trip/</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>MCP compatibility</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>Serving legacy clients, MCP Python SDK</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>官方 SDK 文档</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>按需</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>同一 server 兼容两代及代际分叉位置</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G55" s="19" t="inlineStr">
         <is>
           <t>https://py.sdk.modelcontextprotocol.io/run/legacy-clients/</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>W15</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>MCP Inspector</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>MCP Inspector</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>官方工具文档</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>现代/旧版协商、stdio 调试与消息检查</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G56" s="20" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/docs/2026-07-28/tools/inspector</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>VS Code Codex MCP</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Model Context Protocol, Codex</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>OpenAI 官方文档</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>在 IDE 扩展中配置、信任、调用、禁用和移除本地 MCP server</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>https://learn.chatgpt.com/docs/extend/mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>VS Code Codex Skills</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Build skills, Codex</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>OpenAI 官方文档</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>在 IDE 扩展中核对 SKILL.md、触发、资源加载、scope 与禁用边界</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>https://learn.chatgpt.com/docs/build-skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Cline Rules</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Rules, Cline</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>核对 AGENTS.md 识别、scope、启停与项目规则边界</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/customization/cline-rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Cline MCP</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>MCP, Cline</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Hands-on</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>VS Code 中配置 stdio server，观察调用、权限、启停、日志与移除</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/mcp/mcp-overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Cline Skills</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Skills, Cline</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>条件项</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>核对 progressive disclosure、scope、触发与禁用；仅在已安装版本提供入口时实践</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/customization/skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>Agent evals</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>Evaluate agent workflows, OpenAI API</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>官方文档</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>trace grading、workflow-level error 与可复现评估</t>
         </is>
       </c>
-      <c r="G44" s="20" t="inlineStr">
+      <c r="G62" s="20" t="inlineStr">
         <is>
           <t>https://developers.openai.com/api/docs/guides/agent-evals</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>Agent evals</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>Demystifying evals for AI agents</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>task、trial、grader、trajectory 与 outcome 分层</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/demystifying-evals-for-ai-agents</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>Effective context engineering for AI agents</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t>必读</t>
-        </is>
-      </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>prompt、tools、retrieval、history 与 context budget</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="G64" s="20" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/effective-context-engineering-for-ai-agents</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Production architecture</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>Scaling Managed Agents: Decoupling the brain from the hands</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>官方工程文章</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>认知</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>session、sandbox、durable event log 与凭据隔离的生产视角</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G65" s="19" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/engineering/managed-agents</t>
         </is>
       </c>
     </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>AI SDLC</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>Building an AI-Native Engineering Team</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>官方指南</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>核心入口</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>coding agents 贯穿 plan/design/build/test/review/operations，工程师保留所有权</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>https://learn.chatgpt.com/guides/build-ai-native-engineering-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Scheduling, Cline</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>官方文档</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>认知</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>理解 schedule 生命周期与历史；文档明确不适用于 VS Code，hands-on 使用 multi-trial runner</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>https://docs.cline.bot/cli/scheduling</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G47"/>
+  <autoFilter ref="A4:G67"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
+    <hyperlink ref="G5" r:id="rId1"/>
+    <hyperlink ref="G6" r:id="rId2"/>
+    <hyperlink ref="G7" r:id="rId3"/>
+    <hyperlink ref="G8" r:id="rId4"/>
+    <hyperlink ref="G9" r:id="rId5"/>
+    <hyperlink ref="G10" r:id="rId6"/>
+    <hyperlink ref="G11" r:id="rId7"/>
+    <hyperlink ref="G12" r:id="rId8"/>
+    <hyperlink ref="G13" r:id="rId9"/>
+    <hyperlink ref="G14" r:id="rId10"/>
+    <hyperlink ref="G15" r:id="rId11"/>
+    <hyperlink ref="G16" r:id="rId12"/>
+    <hyperlink ref="G17" r:id="rId13"/>
+    <hyperlink ref="G18" r:id="rId14"/>
+    <hyperlink ref="G19" r:id="rId15"/>
+    <hyperlink ref="G24" r:id="rId16"/>
+    <hyperlink ref="G25" r:id="rId17"/>
+    <hyperlink ref="G26" r:id="rId18"/>
+    <hyperlink ref="G27" r:id="rId19"/>
+    <hyperlink ref="G28" r:id="rId20"/>
+    <hyperlink ref="G29" r:id="rId21"/>
+    <hyperlink ref="G30" r:id="rId22"/>
+    <hyperlink ref="G31" r:id="rId23"/>
+    <hyperlink ref="G32" r:id="rId24"/>
+    <hyperlink ref="G33" r:id="rId25"/>
+    <hyperlink ref="G34" r:id="rId26"/>
+    <hyperlink ref="G35" r:id="rId27"/>
+    <hyperlink ref="G36" r:id="rId28"/>
+    <hyperlink ref="G37" r:id="rId29"/>
+    <hyperlink ref="G38" r:id="rId30"/>
+    <hyperlink ref="G39" r:id="rId31"/>
+    <hyperlink ref="G40" r:id="rId32"/>
+    <hyperlink ref="G41" r:id="rId33"/>
+    <hyperlink ref="G42" r:id="rId34"/>
+    <hyperlink ref="G43" r:id="rId35"/>
+    <hyperlink ref="G44" r:id="rId36"/>
+    <hyperlink ref="G45" r:id="rId37"/>
+    <hyperlink ref="G46" r:id="rId38"/>
+    <hyperlink ref="G47" r:id="rId39"/>
+    <hyperlink ref="G48" r:id="rId40"/>
+    <hyperlink ref="G49" r:id="rId41"/>
+    <hyperlink ref="G50" r:id="rId42"/>
+    <hyperlink ref="G51" r:id="rId43"/>
+    <hyperlink ref="G52" r:id="rId44"/>
+    <hyperlink ref="G53" r:id="rId45"/>
+    <hyperlink ref="G54" r:id="rId46"/>
+    <hyperlink ref="G55" r:id="rId47"/>
+    <hyperlink ref="G56" r:id="rId48"/>
+    <hyperlink ref="G57" r:id="rId49"/>
+    <hyperlink ref="G58" r:id="rId50"/>
+    <hyperlink ref="G59" r:id="rId51"/>
+    <hyperlink ref="G60" r:id="rId52"/>
+    <hyperlink ref="G61" r:id="rId53"/>
+    <hyperlink ref="G62" r:id="rId54"/>
+    <hyperlink ref="G63" r:id="rId55"/>
+    <hyperlink ref="G64" r:id="rId56"/>
+    <hyperlink ref="G65" r:id="rId57"/>
+    <hyperlink ref="G66" r:id="rId58"/>
+    <hyperlink ref="G67" r:id="rId59"/>
+    <hyperlink ref="G20" r:id="rId60"/>
+    <hyperlink ref="G21" r:id="rId61"/>
+    <hyperlink ref="G22" r:id="rId62"/>
+    <hyperlink ref="G23" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>

--- a/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
+++ b/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
@@ -781,7 +781,7 @@
         <is>
           <t>W12
 8/31-9/4
-5 天</t>
+4 个有效学习日</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -803,14 +803,14 @@
 • task、timeout、cancellation、pytest
 • HTTP/streaming 与结构化输入输出
 • Prompt 的 instructions/input/examples/context/output 边界与版本
-• Bub turn/hook/tape/context、model/tool/channel
+• Bub turn、tape -&gt; context、model/tool/harness；hook 只跟主链
 • VS Code Codex/Cline 的 context、规则、权限、计划与验证面</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>• 建立项目基线与冒烟测试
-• 冻结 Bub、DeepSeek Harness 来源版本
+• 冻结 Bub 来源版本
 • 在 VS Code 记录 Codex/Cline 版本、provider、权限与 AGENTS.md 加载
 • 跟踪 Bub 一次完整 turn 主链并写阅读报告
 • 建立版本化 prompt v0
@@ -838,7 +838,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="224" customHeight="1">
+    <row r="10" ht="244" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>W13
@@ -870,6 +870,7 @@
       <c r="E10" s="11" t="inlineStr">
         <is>
           <t>• 出题前冻结 Tier A/Tier B corpus、commit 与排除规则
+• 计量 token 并先跑可容纳语料的 full-context 必要性门禁
 • 本人冻结题目、标签、指标、阈值和通过标准
 • 建立 full-context 质量上限锚点
 • 分别跑通 BM25 与 dense 基线
@@ -931,13 +932,14 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>• 本人冻结工具语义、预算、停止/停滞、state/memory policy、verifier 与 eval task
+          <t>• 同题先跑单次模型 + retrieval 或固定 workflow 非 Agent 基线
+• 本人冻结工具语义、预算、停止/停滞、state/memory policy、verifier 与 eval task
 • 实现只读 retrieval tool 与最小 harness
 • 对冻结 dev task 只改变一个 prompt 因素并重跑相同 eval
 • 完成有界 session state 的 write/read/reset/isolation 与一次 context compaction/eviction 观察
 • 落盘脱敏 trace，完成 deterministic replay 与多 trial
-• 对照抽样 DeepSeek Harness
-• 条件项：OpenAI Agents SDK spike，最多半天</t>
+• 自建后用 60-90 分钟对照 OpenAI Agents SDK 的 runtime 职责
+• 条件项：凭据与网络可用时运行最小 SDK 单工具任务</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -951,8 +953,8 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>不做 multi-agent、持久/向量 memory、写工具或自动部署。
-Prompt + session state/context 实验合计半天；超时先砍 SDK spike 与额外源码抽样。
+          <t>不做 multi-agent、持久/向量 memory、写工具、通用 framework、多 provider 抽象或自动部署。
+SDK 职责对照必做；真实 SDK run 可因凭据/网络失败停止。自建 harness 只作为教学实现。
 交接：只读 tool + trace + verifier + session reset/isolation。</t>
         </is>
       </c>
@@ -1031,7 +1033,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>将 RAG、Agent 与 MCP 串成可观察、可归因、可回归的最小链路，并掌握 Prompt/memory 回归、运行调度与 AI SDLC。</t>
+          <t>收口从 W13 开始积累的 eval 与 trace，将 RAG、Agent 与 MCP 串成可观察、可归因、可回归的最小链路。</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -2038,12 +2040,12 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>Spike</t>
+          <t>必做职责对照</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>半天 compatibility spike 的 SDK 入口</t>
+          <t>自建后用 60-90 分钟对照 loop、state、tool execution 与 trace；真实 run 条件执行</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -2122,7 +2124,7 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/engineering/building-effective-agents</t>
+          <t>https://www.anthropic.com/research/building-effective-agents</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2252,7 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>Effective harnesses for long-running agents</t>
+          <t>Harness design for long-running apps</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -2270,7 +2272,7 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/engineering/effective-harnesses-for-long-running-agents</t>
+          <t>https://www.anthropic.com/engineering/harness-design-long-running-apps</t>
         </is>
       </c>
     </row>
@@ -2393,32 +2395,32 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Harness reference</t>
+          <t>Agent runtime</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>DeepSeek Harness</t>
+          <t>Running agents, OpenAI API</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>官方项目</t>
+          <t>官方文档</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>实验查阅</t>
+          <t>必做职责对照</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>developer preview 项目入口；执行时锁定 commit</t>
+          <t>agent loop、state continuation、tool execution 与停止条件</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/deepseek-harness</t>
+          <t>https://developers.openai.com/api/docs/guides/agents/running-agents</t>
         </is>
       </c>
     </row>
@@ -2430,32 +2432,32 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Harness reference</t>
+          <t>Trace and evals</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>DeepSeek Harness Architecture</t>
+          <t>Trace grading, OpenAI API</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>官方项目文档</t>
+          <t>官方文档</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>按需</t>
+          <t>实验查阅</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>plugin、model、tool、session 与 agent-loop 架构</t>
+          <t>端到端 trace 的结构化评分、失败定位与回归比较</t>
         </is>
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/deepseek-harness/blob/master/docs/architecture.md</t>
+          <t>https://developers.openai.com/api/docs/guides/trace-grading</t>
         </is>
       </c>
     </row>

--- a/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
+++ b/plan/AI_Engineer_Reskill_5_Week_Plan_20260831.xlsx
@@ -631,30 +631,30 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="16"/>
+    <col customWidth="1" max="2" min="2" width="24"/>
+    <col customWidth="1" max="3" min="3" width="34"/>
+    <col customWidth="1" max="4" min="4" width="47"/>
+    <col customWidth="1" max="5" min="5" width="50"/>
+    <col customWidth="1" max="6" min="6" width="45"/>
+    <col customWidth="1" max="7" min="7" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row customHeight="1" ht="38" r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI Engineer Reskill 五周学习计划</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row customHeight="1" ht="24" r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>W12-W16  |  Python -&gt; RAG -&gt; Single-Agent Harness -&gt; MCP -&gt; Reliability &amp; Evals</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row customHeight="1" ht="26" r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>计划周期</t>
@@ -671,7 +671,7 @@
       <c r="F3" s="18" t="n"/>
       <c r="G3" s="18" t="n"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row customHeight="1" ht="26" r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>能力主线</t>
@@ -688,7 +688,7 @@
       <c r="F4" s="18" t="n"/>
       <c r="G4" s="18" t="n"/>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row customHeight="1" ht="26" r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>统一实践场景</t>
@@ -705,7 +705,7 @@
       <c r="F5" s="18" t="n"/>
       <c r="G5" s="18" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row customHeight="1" ht="34" r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>执行基线</t>
@@ -722,7 +722,7 @@
       <c r="F6" s="18" t="n"/>
       <c r="G6" s="18" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row customHeight="1" ht="34" r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>横切重点</t>
@@ -739,7 +739,7 @@
       <c r="F7" s="18" t="n"/>
       <c r="G7" s="18" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row customHeight="1" ht="30" r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>周次 / 日期</t>
@@ -776,7 +776,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="244" customHeight="1">
+    <row customHeight="1" ht="244" r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>W12
@@ -834,11 +834,11 @@
         <is>
           <t>不进入 RAG、完整 Agent loop、MCP 或 UI。
 实操只使用已安装的 VS Code Codex 26.5825.51511 与 Cline 4.1.16；Claude Code 受防火墙限制，Codex App 不支持 Intel，均不作为依赖。
-两端同题 hands-on 必做，总投入 60-90 分钟。交接：Python/model client 可运行；prompt v0 已版本化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="244" customHeight="1">
+两端同题 hands-on 必做，总投入 60-90 分钟。交接：Python/model client 可运行；prompt v0 已版本化，但它是无 retrieval 的用户注册信息提取 Prompt，只作为版本管理基线；Tier A 七份清单与排除类别已确认，物理快照留到 W13。</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="244" r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>W13
@@ -853,53 +853,49 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>在冻结语料与 held-out 题集上分离 retrieval 和 generation，比较质量、成本与延迟。</t>
+          <t>在冻结 corpus 与 holdout set 上，独立实现、解释并评测可重复运行的最小 RAG 链路，分离 retrieval、context assembly、prompt 与 generation 的质量、成本和延迟。</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>• ingestion、预处理、chunking、metadata
-• full-context、中文 BM25、dense retrieval
-• multilingual-e5-small、中文回退候选与 Intel x86 runtime 门禁
-• grounding prompt、citation、abstention、context budget
-• RAG knowledge 与 Agent memory 的职责差异
-• dev/holdout 隔离与逐题失败分析
+          <t>• corpus snapshot、provenance、token 与 context budget
+• ingestion、preprocessing、chunking、metadata
+• full-context、中文 BM25 与 dense retrieval
+• context assembly、grounded generation、citation 与 abstention
+• dev/holdout 隔离与逐题 failure attribution
+• RAG、session state、durable memory 与 trace 的职责边界
 • hybrid/RRF 仅作条件项</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>• 出题前冻结 Tier A/Tier B corpus、commit 与排除规则
-• 计量 token 并先跑可容纳语料的 full-context 必要性门禁
-• 本人冻结题目、标签、指标、阈值和通过标准
-• 建立 full-context 质量上限锚点
-• 分别跑通 BM25 与 dense 基线
-• 复用 Python 3.12，以 onnxruntime==1.23.2 + 发布者 fp32 文件验证 x86 基线；torch==2.2.2 仅作兼容回退
-• 冻结 wheel/hash、runtime/model revision、E5 前缀/归一化/截断，并记录冷启动、吞吐、p50/p95、峰值 RSS 与全量估算
-• 量化仅作同一冻结小样本的条件对照
-• 冻结 grounding/citation/abstention prompt 边界
-• 记录 retrieval、context assembly、prompt、generation 的逐题失败与成本
-• 收口时运行一次 holdout</t>
+          <t>• 第一题 eval 前冻结 Tier A snapshot、commit 与 manifest；Tier B 仅作独立条件扩展
+• 计量 token、确认 context fit，并由本人冻结 eval、RAG Prompt 与通过标准
+• 完成 full-context 门禁：Tier A 可容纳时运行 baseline，不可容纳时保留容量证据
+• 完成可追溯的 BM25 retrieval 与端到端 RAG；BM25 稳定后才启动 dense runtime 门禁和同集对照
+• 冻结 corpus、eval、Prompt、model 与 runtime 版本，记录质量、延迟、token、成本和逐题归因
+• 仅在稳定实现与配置已冻结后首次运行 holdout，且不据结果调参</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>• 能解释 ingestion -&gt; retrieval -&gt; context -&gt; generation -&gt; eval 边界
-• 不把索引、检索结果、session state 或 trace 混称为 memory
-• 对每道失败题给出 retrieval/context/prompt/generation 分层归因
-• holdout 未被日常调参污染
-• W15 D1 延迟重建确定性 retrieval 数据流</t>
+          <t>• 能解释 corpus -&gt; retrieval -&gt; context assembly -&gt; prompt -&gt; generation -&gt; eval 的职责边界
+• full-context 门禁可复核；同一 Tier A snapshot 与冻结 dev set 可复跑 BM25 RAG 与 dense 对照
+• BM25 端到端链路可独立运行，证据、实际 context、带来源答案或拒答均可观察
+• 逐题分层归因；holdout 仅在门禁通过后首次运行且不据此调参
+• dense 未完成时如实标记，不把 W14 可继续等同于 W13 完整通过
+• 本人完成独立讲解与 W15 D1 retrieval 确定性数据流重建入口</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>reranker、GraphRAG、向量数据库和本地生成模型不进入主线。
-只使用已核对到 CPython 3.12/macOS x86_64 wheel 的固定版本；不解析到最新版、不源码编译。安装或资源/质量门失败时改用 embedding API，BM25 与冻结 eval 保留，dense 不阻塞 W14。
-交接：可用 BM25 入口 + 冻结 eval。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="248" customHeight="1">
+          <t>reranker、GraphRAG、向量数据库和本地生成模型不进入主线；Tier B、hybrid/RRF、量化和第二 embedding 模型均为条件项。
+dense 首选 onnxruntime==1.23.2 + 发布者 fp32 文件，torch==2.2.2 仅作兼容回退；不解析到最新版、不源码编译。本地与 API 均不可用时如实标为未完成或未验证，BM25 可交接 W14，但 W13 不算完整通过。
+交接：冻结 corpus/eval，以及稳定可复跑的 BM25 端到端 RAG；包含可观察的检索证据、实际 context、grounding/citation/abstention 和失败归因。</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="248" r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>W14
@@ -959,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="248" customHeight="1">
+    <row customHeight="1" ht="248" r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>W15
@@ -1017,7 +1013,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="238" customHeight="1">
+    <row customHeight="1" ht="238" r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>W16
@@ -1084,8 +1080,8 @@
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins bottom="0.35" footer="0.15" header="0.15" left="0.25" right="0.25" top="0.35"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape" paperSize="8"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Engineer Reskill | W12-W16&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
